--- a/working_with_spreadsheet/template.xlsx
+++ b/working_with_spreadsheet/template.xlsx
@@ -14,9 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>POP tuman IM 11-sinf o'quvchilarining 10-chorak BSB natijalari</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>POP tuman IM 11
+-sinf o'quvchilarining 1
+-chorak 1-bsb
+ natijalari</t>
   </si>
   <si>
     <t>№</t>
@@ -25,19 +28,29 @@
     <t>F.I.SH</t>
   </si>
   <si>
-    <t>DF 100</t>
-  </si>
-  <si>
-    <t>BN 102</t>
-  </si>
-  <si>
-    <t>GH 100</t>
-  </si>
-  <si>
-    <t>Jami: 302</t>
+    <t>Grammar 11</t>
+  </si>
+  <si>
+    <t>Vocab 19</t>
+  </si>
+  <si>
+    <t>Jami: 30</t>
   </si>
   <si>
     <t>Foiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">john
+</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>36.67</t>
   </si>
 </sst>
 </file>
@@ -386,7 +399,6 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="1"/>
@@ -395,7 +407,6 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1"/>
@@ -404,7 +415,6 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
@@ -413,7 +423,6 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
     </row>
     <row r="5" ht="40" customHeight="true">
       <c r="A5" s="2" t="s">
@@ -434,18 +443,26 @@
       <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="2" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
@@ -454,7 +471,6 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
@@ -463,7 +479,6 @@
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
@@ -472,7 +487,6 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
@@ -481,7 +495,6 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
@@ -490,7 +503,6 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
@@ -499,7 +511,6 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
@@ -508,7 +519,6 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
@@ -517,7 +527,6 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
@@ -526,11 +535,10 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G4"/>
+    <mergeCell ref="A1:F4"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/working_with_spreadsheet/template.xlsx
+++ b/working_with_spreadsheet/template.xlsx
@@ -14,11 +14,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>POP tuman IM 11
--sinf o'quvchilarining 1
--chorak 1-bsb
+-sinf o'quvchilarining 2
+-chorak 1-BSB
  natijalari</t>
   </si>
   <si>
@@ -28,29 +28,58 @@
     <t>F.I.SH</t>
   </si>
   <si>
-    <t>Grammar 11</t>
-  </si>
-  <si>
-    <t>Vocab 19</t>
-  </si>
-  <si>
-    <t>Jami: 30</t>
+    <t>Vocabulary 8</t>
+  </si>
+  <si>
+    <t>Grammar 5</t>
+  </si>
+  <si>
+    <t>Reading 5</t>
+  </si>
+  <si>
+    <t>Writing 7</t>
+  </si>
+  <si>
+    <t>Jami: 25</t>
   </si>
   <si>
     <t>Foiz</t>
   </si>
   <si>
-    <t xml:space="preserve">john
+    <t xml:space="preserve">Fayozbek Erkinjonov
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Sadriddin Sayfiddinov
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azizbek Hasanboy
+</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>36.67</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>80</t>
   </si>
 </sst>
 </file>
@@ -399,6 +428,8 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="1"/>
@@ -407,6 +438,8 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1"/>
@@ -415,6 +448,8 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
@@ -423,6 +458,8 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" ht="40" customHeight="true">
       <c r="A5" s="2" t="s">
@@ -443,42 +480,90 @@
       <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="1">
+        <v>13</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="1">
+        <v>21</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1">
+        <v>20</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
@@ -487,6 +572,8 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
@@ -495,6 +582,8 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
@@ -503,6 +592,8 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
@@ -511,6 +602,8 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
@@ -519,6 +612,8 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
@@ -527,6 +622,8 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
@@ -535,10 +632,12 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="A1:H4"/>
   </mergeCells>
 </worksheet>
 </file>